--- a/api/FT8TW-API.xlsx
+++ b/api/FT8TW-API.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capabilities" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Endpoints'!$A$1:$M$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Endpoints'!$A$1:$M$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -655,7 +655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -901,7 +901,7 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>input.level</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -921,17 +921,17 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>Operating state: mode, callsign, grid, band, audio frequency, whether it is decoding or transmitting, the current target callsign, and the sequence numbers currently held in the event buffer.</t>
+          <t>Operating state: mode, callsign, grid, band, audio frequency, whether it is decoding or transmitting, the current target callsign, the sequence numbers currently held in the event buffer, and inputLevel — the receive audio level for the slot that just finished (rmsDb, peakDb, clipPercent and crestFactorDb).</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>運作狀態：模式、呼號、網格、波段、音訊頻率、是否正在解碼或發射、目前的呼叫對象，以及事件緩衝區目前持有的序號範圍。</t>
+          <t>運作狀態：模式、呼號、網格、波段、音訊頻率、是否正在解碼或發射、目前的呼叫對象、事件緩衝區目前持有的序號範圍，以及 inputLevel——剛結束的那個時序的接收音訊電平（rmsDb、peakDb、clipPercent、crestFactorDb）。</t>
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>latestSeq / oldestSeq 可用來判斷增量查詢的游標是否還在緩衝區內。</t>
+          <t>latestSeq / oldestSeq 可用來判斷增量查詢的游標是否還在緩衝區內。 inputLevel.available is false during transmit slots and in acoustic mode — 那時沒有可用的讀數，rmsDb 等欄位不會出現，不要當成 0 處理。 targetSetBy is 'api' or 'local': the phone and the API can both change the target and the last write wins — there is deliberately no locking, because the phone must stay in ultimate control. Watch this field to notice that the operator has taken over（外掛設了呼叫 A、使用者在手機上改成 B，不看這個欄位就會繼續按著 A 的劇本跑）。</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>/api/v1/rig</t>
+          <t>/api/v1/bands</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>rig.status</t>
+          <t>bands.list</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -1116,17 +1116,17 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>Radio state: model, control and connection mode, frequency, SWR, power, PTT.</t>
+          <t>Frequencies available in the current mode, with the display name the app shows and a flag for the one in use. POST /control/band only accepts values from this list, so query it first rather than assuming the standard FT8 frequencies — users can define their own frequency table.</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>電台狀態：型號、控制與連線方式、頻率、SWR、功率、PTT。</t>
+          <t>目前模式可用的頻率清單，含 App 畫面上顯示的名稱與「目前使用中」標記。POST /control/band 只接受這份清單裡的值，因此請先查詢，不要假設標準的 FT8 頻率——使用者可以自訂頻率表。</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>Values the radio does not report come back as null, never 0 — 外掛拿到 0 會以為是真實讀數。SWR 小於 1.0 代表該機從未回報過。</t>
+          <t>The list changes with the mode（FT8／FT4／FT2 各有一份），切換模式後要重新查。</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>/api/v1/logs</t>
+          <t>/api/v1/rig</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>since, limit, tag, level</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>logs</t>
+          <t>rig.status</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>Application debug log. Same cursor semantics as /messages.</t>
+          <t>Radio state: model, control and connection mode, frequency, SWR, power, PTT.</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>App 的除錯訊息。游標語意與 /messages 相同。</t>
+          <t>電台狀態：型號、控制與連線方式、頻率、SWR、功率、PTT。</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>tag / level 過濾會在截斷之前套用，因此 limit 拿到的是過濾後的筆數。</t>
+          <t>Values the radio does not report come back as null, never 0 — 外掛拿到 0 會以為是真實讀數。SWR 小於 1.0 代表該機從未回報過。</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>/api/v1/spectrum</t>
+          <t>/api/v1/logs</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>denoise (0/1)</t>
+          <t>since, limit, tag, level</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>spectrum</t>
+          <t>logs</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1246,17 +1246,17 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>Current audio spectrum for drawing a waterfall. The FFT is computed per request, so it costs nothing while nobody is asking, and it does not require the user to be on the app's own spectrum screen.</t>
+          <t>Application debug log. Same cursor semantics as /messages.</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>目前的音訊頻譜，供外部畫瀑布圖。FFT 是按需計算，沒有請求就沒有成本，也不需要使用者停留在 App 的頻譜畫面。</t>
+          <t>App 的除錯訊息。游標語意與 /messages 相同。</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>Use binHz to convert bin index to Hz — 不要自己猜 FFT 大小。數值已套用 App 的瀑布圖 AGC（0-255 顯示等級），再拉伸一次會抬高雜訊。</t>
+          <t>tag / level 過濾會在截斷之前套用，因此 limit 拿到的是過濾後的筆數。</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>/api/v1/callsign/{callsign}</t>
+          <t>/api/v1/spectrum</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>denoise (0/1)</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>callsign.lookup</t>
+          <t>spectrum</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -1311,17 +1311,17 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>What the app knows about a callsign: country, grid, distance, and whether it is already in the log.</t>
+          <t>Current audio spectrum for drawing a waterfall. The FFT is computed per request, so it costs nothing while nobody is asking, and it does not require the user to be on the app's own spectrum screen.</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>App 對某個呼號所知的資訊：國家、網格、距離，以及是否已在通聯記錄中。</t>
+          <t>目前的音訊頻譜，供外部畫瀑布圖。FFT 是按需計算，沒有請求就沒有成本，也不需要使用者停留在 App 的頻譜畫面。</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>Grid comes from the app's own CallsignQTH cache — 沒有查過的呼號會回 null。</t>
+          <t>Use binHz to convert bin index to Hz — 不要自己猜 FFT 大小。數值已套用 App 的瀑布圖 AGC（0-255 顯示等級），再拉伸一次會抬高雜訊。</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>/api/v1/config</t>
+          <t>/api/v1/callsign/{callsign}</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>config.read</t>
+          <t>callsign.lookup</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -1376,17 +1376,17 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>Selected settings, by whitelist. Only explicitly listed keys are exposed.</t>
+          <t>What the app knows about a callsign: country, grid, distance, and whether it is already in the log.</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>部分設定值，採白名單。只有明確列出的鍵才會出現。</t>
+          <t>App 對某個呼號所知的資訊：國家、網格、距離，以及是否已在通聯記錄中。</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>Whitelist, not blacklist — 用黑名單的話，日後新增一個含密碼的設定就會自動外洩且無人察覺。第三方憑證（Cloudlog、QRZ）永遠不在其中。</t>
+          <t>Grid comes from the app's own CallsignQTH cache — 沒有查過的呼號會回 null。</t>
         </is>
       </c>
     </row>
@@ -1401,12 +1401,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>/api/v1/stream</t>
+          <t>/api/v1/config</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>events (decode,rig,qso,log,status), since, token</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>stream.sse</t>
+          <t>config.read</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1441,17 +1441,17 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Server-sent events. Each subscriber gets an independent queue, so multiple clients receive every event rather than sharing them out.</t>
+          <t>Selected settings, by whitelist. Only explicitly listed keys are exposed.</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>事件串流（SSE）。每個訂閱者有獨立佇列，多個客戶端各自收到完整事件，不會互相瓜分。</t>
+          <t>部分設定值，採白名單。只有明確列出的鍵才會出現。</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>EventSource cannot set headers, so this endpoint also accepts ?token= （瀏覽器規格限制）。收到 dropped 事件代表你的客戶端跟不上產生速度。</t>
+          <t>Whitelist, not blacklist — 用黑名單的話，日後新增一個含密碼的設定就會自動外洩且無人察覺。第三方憑證（Cloudlog、QRZ）永遠不在其中。</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>/api/v1/map/tile/{z}/{x}/{y}</t>
+          <t>/api/v1/stream</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>token</t>
+          <t>events (decode,rig,qso,log,status), since, token</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>map.tiles</t>
+          <t>stream.sse</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1506,17 +1506,17 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>Offline world map tile (JPEG) from the archive bundled in the app, so a map works with no internet connection. Zoom 0-4 only.</t>
+          <t>Server-sent events. Each subscriber gets an independent queue, so multiple clients receive every event rather than sharing them out.</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>離線世界地圖圖磚（JPEG），來自 App 內建的圖磚檔，沒有網路也能畫地圖。僅支援 zoom 0-4。</t>
+          <t>事件串流（SSE）。每個訂閱者有獨立佇列，多個客戶端各自收到完整事件，不會互相瓜分。</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>Accepts ?token= so it can be used directly as an &lt;img&gt; source。此端點刻意不寫入稽核記錄，否則十幾個圖磚請求會把真正該看的存取洗掉。</t>
+          <t>EventSource cannot set headers, so this endpoint also accepts ?token= （瀏覽器規格限制）。收到 dropped 事件代表你的客戶端跟不上產生速度。</t>
         </is>
       </c>
     </row>
@@ -1531,17 +1531,17 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>/api/v1/audit</t>
+          <t>/api/v1/map/tile/{z}/{x}/{y}</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>limit</t>
+          <t>token</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>readonly</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>audit.read</t>
+          <t>map.tiles</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>Recent API access log, newest first. Requires a full-access token because entries contain each caller's IP and access history. NOT gated by the remote-control switch: being unable to look at what just happened right after switching remote control off would be exactly the wrong behaviour.</t>
+          <t>Offline world map tile (JPEG) from the archive bundled in the app, so a map works with no internet connection. Zoom 0-4 only.</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>近期的 API 存取記錄，由新到舊。需要 full token，因為記錄含每個呼叫者的 IP 與存取歷史。不受遠端控制開關影響：使用者發現異狀而關掉遠端控制之後，正是最需要查得到剛才發生什麼的時候。</t>
+          <t>離線世界地圖圖磚（JPEG），來自 App 內建的圖磚檔，沒有網路也能畫地圖。僅支援 zoom 0-4。</t>
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>Ring buffer of 200 — held == capacity 表示更早的存取已被丟棄，這份清單不是完整歷史。讀取本身會被記錄，因此不要輪詢。</t>
+          <t>Accepts ?token= so it can be used directly as an &lt;img&gt; source。此端點刻意不寫入稽核記錄，否則十幾個圖磚請求會把真正該看的存取洗掉。</t>
         </is>
       </c>
     </row>
@@ -1596,120 +1596,120 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
+          <t>/api/v1/audit</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>limit</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>audit.read</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>26.0801</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>Recent API access log, newest first. Requires a full-access token because entries contain each caller's IP and access history. NOT gated by the remote-control switch: being unable to look at what just happened right after switching remote control off would be exactly the wrong behaviour.</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>近期的 API 存取記錄，由新到舊。需要 full token，因為記錄含每個呼叫者的 IP 與存取歷史。不受遠端控制開關影響：使用者發現異狀而關掉遠端控制之後，正是最需要查得到剛才發生什麼的時候。</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>Ring buffer of 200 — held == capacity 表示更早的存取已被丟棄，這份清單不是完整歷史。讀取本身會被記錄，因此不要輪詢。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="86" customHeight="1">
+      <c r="A16" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
           <t>/api/v1/openapi.json</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>readonly</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>26.0801</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>Machine-readable OpenAPI description of this API.</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>本 API 的 OpenAPI 描述（機器可讀）。</t>
         </is>
       </c>
-      <c r="M15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16" ht="86" customHeight="1">
-      <c r="A16" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>/api/v1/tx/stop</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>— (empty body)</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>control.tx</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>26.0801</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>Supported</t>
-        </is>
-      </c>
-      <c r="K16" s="6" t="inlineStr">
-        <is>
-          <t>Stop transmitting. Succeeds in EVERY state, including when nothing is transmitting and when the transmitter is not initialised — the caller's goal (nothing on the air) is already met, so that is not an error. Use the 'changed' field to tell 'I stopped a transmission' from 'nothing was running'.</t>
-        </is>
-      </c>
-      <c r="L16" s="6" t="inlineStr">
-        <is>
-          <t>停止發射。任何狀態下都成功，包含本來就沒在發射、以及發射器尚未初始化——呼叫者要的條件（沒有東西在空中）那時已經滿足，回錯誤只會讓對方重試。用 changed 欄位分辨「停下了一個發射」與「本來就沒在發」。</t>
-        </is>
-      </c>
-      <c r="M16" s="6" t="inlineStr">
-        <is>
-          <t>Stop must never fail on a precondition — 那會讓它在最需要的時候不能用。</t>
-        </is>
-      </c>
+      <c r="M16" s="4" t="inlineStr"/>
     </row>
     <row r="17" ht="86" customHeight="1">
       <c r="A17" s="6" t="n">
@@ -1722,127 +1722,521 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
+          <t>/api/v1/tx/stop</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>— (empty body)</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>control.tx</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>26.0801</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>Stop transmitting. Succeeds in EVERY state, including when nothing is transmitting and when the transmitter is not initialised — the caller's goal (nothing on the air) is already met, so that is not an error. Use the 'changed' field to tell 'I stopped a transmission' from 'nothing was running'.</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>停止發射。任何狀態下都成功，包含本來就沒在發射、以及發射器尚未初始化——呼叫者要的條件（沒有東西在空中）那時已經滿足，回錯誤只會讓對方重試。用 changed 欄位分辨「停下了一個發射」與「本來就沒在發」。</t>
+        </is>
+      </c>
+      <c r="M17" s="6" t="inlineStr">
+        <is>
+          <t>Stop must never fail on a precondition — 那會讓它在最需要的時候不能用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="86" customHeight="1">
+      <c r="A18" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
           <t>/api/v1/tx/activate</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>body: {"activated": true|false}</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>full</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>control.tx</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>26.0801</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="J17" s="6" t="inlineStr">
+      <c r="J18" s="6" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="K17" s="6" t="inlineStr">
+      <c r="K18" s="6" t="inlineStr">
         <is>
           <t>Enable or disable transmission. The 'activated' field is required and is never defaulted — guessing it would start a transmission on a malformed request. The response reports the ACTUAL state, not the request: the app can refuse (for example while a mandatory update is pending), in which case 'blocked' is true.</t>
         </is>
       </c>
-      <c r="L17" s="6" t="inlineStr">
+      <c r="L18" s="6" t="inlineStr">
         <is>
           <t>開啟或關閉發射。activated 欄位為必填且不套用預設值——猜成 true 會讓一個打錯的請求開始發射。回應帶的是實際狀態而非請求值：App 可能拒絕（例如必要更新尚未完成），此時 blocked 為 true。</t>
         </is>
       </c>
-      <c r="M17" s="6" t="inlineStr">
+      <c r="M18" s="6" t="inlineStr">
         <is>
           <t>Goes through the app's own state machine, so it inherits every guard already there — 不自行改旗標。</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="86" customHeight="1">
-      <c r="A18" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
+    <row r="19" ht="86" customHeight="1">
+      <c r="A19" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/tx/call</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>body: {"callsign": "JA1ABC", "activate": false}</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>control.tx</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>26.0801</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>Set the station to call. Only accepts a callsign that actually appears in the recent decodes — you can only call a station the app has heard. The slot, audio frequency and signal report are taken from that decode, so the caller supplies only the callsign.
+Does NOT start transmitting by default; pass activate:true for that.</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>設定呼叫對象。只接受最近解碼中確實出現過的呼號——只能呼叫 App 實際聽到的電台。時序、音訊頻率與信號報告都取自那則解碼，呼叫者只需要給呼號。
+預設&lt;b&gt;不&lt;/b&gt;開始發射，需要時帶 activate:true。</t>
+        </is>
+      </c>
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>Allowing an arbitrary string would let one typo transmit at a station that is not there — 那不只是無效發射。回 bad_request 時訊息會說明是「沒聽到這個呼號」而非格式錯誤，呼叫者才知道該等下一輪解碼。遙測與自由文字訊息不可呼叫，與解碼畫面的規則相同。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="86" customHeight="1">
+      <c r="A20" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/tx/cq</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>body: {"activate": false}</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>control.tx</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>26.0801</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>Go back to calling CQ. Does NOT start transmitting by default; pass activate:true for that.</t>
+        </is>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>回到呼叫 CQ。預設&lt;b&gt;不&lt;/b&gt;開始發射，需要時帶 activate:true。</t>
+        </is>
+      </c>
+      <c r="M20" s="6" t="inlineStr">
+        <is>
+          <t>Fails with busy if no callsign is configured in the app — resetToCQ() 在那種情況下會靜默跳過，回 ok 會讓呼叫者以為設定成功了。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="86" customHeight="1">
+      <c r="A21" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/control/band</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>body: {"band": 14074000}</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>control.radio</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>26.0801</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>Change the operating frequency. Only accepts a frequency that exists in the band list for the current mode — allowing an arbitrary value would let a plugin put the radio outside the amateur bands, and the radio may well comply. Follows exactly the same path as the app's own frequency dialog, so it introduces no new per-model CAT risk. Refused while transmitting: changing frequency mid-transmission moves the carrier while it is on the air.</t>
+        </is>
+      </c>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>切換操作頻率。只接受目前模式的波段清單中存在的頻率——允許任意值等於讓外掛把電台調到業餘頻段之外，而電台可能照做。走與 App 頻率清單完全相同的路徑，因此不會引入新的機型風險。發射中拒絕：發射途中改頻率會讓載波在空中位移。</t>
+        </is>
+      </c>
+      <c r="M21" s="6" t="inlineStr">
+        <is>
+          <t>radioCommanded tells you whether the radio was actually commanded — VOX/藍牙模式下 App 只改自己的設定，使用者仍須手動轉電台，不講清楚會以為換好了。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="86" customHeight="1">
+      <c r="A22" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/control/mode</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>body: {"mode": "FT8"}</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>control.radio</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>26.0801</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>Switch between FT8, FT4 and FT2. This is the app's timing mode and sends no command to the radio, but it DOES change the operating frequency: each mode has its own band list and the nearest entry is selected. The response carries the resulting frequency so the caller need not guess. Refused while transmitting.</t>
+        </is>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>切換 FT8／FT4／FT2。這是 App 內部的時序模式，不對電台送出指令，但會連帶改變操作頻率：各模式的波段清單不同，切換後會挑最接近的那一個。回應帶回新頻率，呼叫者不必自己猜。發射中拒絕。</t>
+        </is>
+      </c>
+      <c r="M22" s="6" t="inlineStr">
+        <is>
+          <t>Changing the timing mode mid-transmission would truncate the signal — 時序模式決定發射的長度與邊界。 CAUTION: switching modes back and forth DRIFTS the frequency. The nearest entry in the new mode's band list is chosen, so FT8 14.074 → FT4 → FT2 → FT8 lands on 14.090, not back on 14.074. This is the app's existing behaviour, not specific to the API — 但透過 API 快速連切會很明顯。Read the 'band' field in the response and set it explicitly with /control/band if you need a particular frequency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="86" customHeight="1">
+      <c r="A23" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/config</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>body: {"key": "antenna", "value": "EFHW 20m"}</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>config.write</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>26.0801</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>Change one setting. The writable list is deliberately much smaller than the readable one — being able to read a value does not mean it is safe for someone else to change it. Writable: noreplylimit, finishretrylimit, antenna.
+One key per request: a batch that half-succeeds leaves a state nobody can describe.</t>
+        </is>
+      </c>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>修改一項設定。可寫清單刻意比可讀清單小得多——能讀不代表別人改掉它是安全的。可寫的是 noreplylimit、finishretrylimit、antenna。
+一次只改一個鍵：批次修改在部分失敗時會留下說不清的中間狀態。</t>
+        </is>
+      </c>
+      <c r="M23" s="6" t="inlineStr">
+        <is>
+          <t>Radio connection settings (model/baudrate/connectmode) are NOT writable — 改了會斷開電台連線而遠端無法接回來，等於自斷後路。callsign 是法規識別、功率上限與 SWR 告警是安全限制、pttdelay 影響發射時序，一律不開放。頻率請用 /control/band（走那裡才會連帶命令電台換頻）。回應的 value 是實際生效的值，可能已被夾到合法範圍內。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="86" customHeight="1">
+      <c r="A24" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>/api/v1/tx/freetext</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>full</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G18" s="9" t="inlineStr">
+      <c r="G24" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>26.0801</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="I24" s="8" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="J24" s="8" t="inlineStr">
         <is>
           <t>Not implemented (by design)</t>
         </is>
       </c>
-      <c r="K18" s="8" t="inlineStr">
+      <c r="K24" s="8" t="inlineStr">
         <is>
           <t>Always returns 501 not_implemented. Free text can put arbitrary content on the air under the licence holder's callsign, and that responsibility cannot be delimited by software. The path is reserved and documented so that plugin authors can tell a deliberate decision from a missing feature.</t>
         </is>
       </c>
-      <c r="L18" s="8" t="inlineStr">
+      <c r="L24" s="8" t="inlineStr">
         <is>
           <t>固定回 501 not_implemented。自由文字可以用執照持有人的呼號送出任意內容，而內容責任無法由軟體界定。此路徑保留並寫入文件，讓外掛作者能分辨「刻意不開放」與「功能還沒做」。</t>
         </is>
       </c>
-      <c r="M18" s="8" t="inlineStr">
+      <c r="M24" s="8" t="inlineStr">
         <is>
           <t>Returning 404 would be read as 'your app is too old' — 那是錯的訊息。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M18"/>
+  <autoFilter ref="A1:M24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1853,7 +2247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2129,64 +2523,86 @@
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>busy</t>
+          <t>conflict</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>409</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>The app did not respond within 2 s. The action may or may not have been applied — query the status and retry.</t>
+          <t>The request is valid but the current state does not allow it (transmitting, or a frequency outside the band list). Satisfy the precondition and retry — the request itself needs no change.</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>App 在 2 秒內沒有回應。動作是否已執行不明，請查詢狀態後重試。</t>
+          <t>請求本身沒問題，但目前狀態不允許（發射中、頻率不在波段清單內）。滿足前提後重試即可，不需要修改請求。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>internal_error</t>
+          <t>busy</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>503</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Unexpected failure.</t>
+          <t>The app did not respond within 2 s. The action may or may not have been applied — query the status and retry.</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>未預期的錯誤。</t>
+          <t>App 在 2 秒內沒有回應。動作是否已執行不明，請查詢狀態後重試。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
+          <t>internal_error</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Unexpected failure.</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>未預期的錯誤。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
           <t>api_disabled</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>403</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>The API is switched off in the app.</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>API 在 App 內被停用。</t>
         </is>
@@ -2203,7 +2619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2401,17 +2817,85 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
+          <t>control.radio</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Band and mode switching</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>切換波段與 FT8/FT4/FT2 模式</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>bands.list</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Available frequencies for the current mode</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>目前模式可用的頻率清單</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>config.write</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Change a whitelisted setting</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>修改白名單內的設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
           <t>audit.read</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>API access log</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>API 存取記錄</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>input.level</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Receive audio level in /status</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>/status 內的接收音訊電平</t>
         </is>
       </c>
     </row>

--- a/api/FT8TW-API.xlsx
+++ b/api/FT8TW-API.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capabilities" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Endpoints'!$A$1:$M$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Endpoints'!$A$1:$M$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -655,7 +655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>/api/v1/rig</t>
+          <t>/api/v1/ui</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>rig.status</t>
+          <t>ui.state</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>Radio state: model, control and connection mode, frequency, SWR, power, PTT.</t>
+          <t>Which screen the app is showing, the visible text on it, and the recent notices it displayed to the operator. The other endpoints answer what the radio is doing; this one answers what the screen says — the red warning line, the toast that just appeared — which is what you cannot see when you are not next to the phone.</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>電台狀態：型號、控制與連線方式、頻率、SWR、功率、PTT。</t>
+          <t>App 目前停在哪個畫面、畫面上看得見的文字，以及最近顯示給操作者的提示。其他端點回答的是電台在做什麼，這一個回答的是畫面上寫了什麼——那行紅字、剛跳出來的提示——也就是人不在手機旁邊時看不到的東西。</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>Values the radio does not report come back as null, never 0 — 外掛拿到 0 會以為是真實讀數。SWR 小於 1.0 代表該機從未回報過。</t>
+          <t>The settings screen needs a FULL token: it displays the complete API tokens and the CloudLog/QRZ keys, so a read-only caller gets only the screen name with redacted:true and a reason. Credentials are redacted on every screen regardless（任何看起來像憑證的長字串一律遮成 ***，不倚賴 id 清單——清單遲早會漏掉新加的欄位，而那種疏漏完全沒有徵兆）。 Input fields are never included: what the user is typing is not what the app is saying. Reading walks the view tree on the main thread, so a busy UI can return 503 busy — 重試即可，這個端點沒有副作用。</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>/api/v1/logs</t>
+          <t>/api/v1/rig</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>since, limit, tag, level</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>logs</t>
+          <t>rig.status</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1246,17 +1246,17 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>Application debug log. Same cursor semantics as /messages.</t>
+          <t>Radio state: model, control and connection mode, frequency, SWR, power, PTT.</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>App 的除錯訊息。游標語意與 /messages 相同。</t>
+          <t>電台狀態：型號、控制與連線方式、頻率、SWR、功率、PTT。</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>tag / level 過濾會在截斷之前套用，因此 limit 拿到的是過濾後的筆數。</t>
+          <t>Values the radio does not report come back as null, never 0 — 外掛拿到 0 會以為是真實讀數。SWR 小於 1.0 代表該機從未回報過。</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>/api/v1/spectrum</t>
+          <t>/api/v1/logs</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>denoise (0/1)</t>
+          <t>since, limit, tag, level</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>spectrum</t>
+          <t>logs</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -1311,17 +1311,17 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>Current audio spectrum for drawing a waterfall. The FFT is computed per request, so it costs nothing while nobody is asking, and it does not require the user to be on the app's own spectrum screen.</t>
+          <t>Application debug log. Same cursor semantics as /messages.</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>目前的音訊頻譜，供外部畫瀑布圖。FFT 是按需計算，沒有請求就沒有成本，也不需要使用者停留在 App 的頻譜畫面。</t>
+          <t>App 的除錯訊息。游標語意與 /messages 相同。</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>Use binHz to convert bin index to Hz — 不要自己猜 FFT 大小。數值已套用 App 的瀑布圖 AGC（0-255 顯示等級），再拉伸一次會抬高雜訊。</t>
+          <t>tag / level 過濾會在截斷之前套用，因此 limit 拿到的是過濾後的筆數。</t>
         </is>
       </c>
     </row>
@@ -1336,12 +1336,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>/api/v1/callsign/{callsign}</t>
+          <t>/api/v1/spectrum</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>denoise (0/1)</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>callsign.lookup</t>
+          <t>spectrum</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -1376,17 +1376,17 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>What the app knows about a callsign: country, grid, distance, and whether it is already in the log.</t>
+          <t>Current audio spectrum for drawing a waterfall. The FFT is computed per request, so it costs nothing while nobody is asking, and it does not require the user to be on the app's own spectrum screen.</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>App 對某個呼號所知的資訊：國家、網格、距離，以及是否已在通聯記錄中。</t>
+          <t>目前的音訊頻譜，供外部畫瀑布圖。FFT 是按需計算，沒有請求就沒有成本，也不需要使用者停留在 App 的頻譜畫面。</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>Grid comes from the app's own CallsignQTH cache — 沒有查過的呼號會回 null。</t>
+          <t>Use binHz to convert bin index to Hz — 不要自己猜 FFT 大小。數值已套用 App 的瀑布圖 AGC（0-255 顯示等級），再拉伸一次會抬高雜訊。</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>/api/v1/config</t>
+          <t>/api/v1/callsign/{callsign}</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>config.read</t>
+          <t>callsign.lookup</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1441,17 +1441,17 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Selected settings, by whitelist. Only explicitly listed keys are exposed.</t>
+          <t>What the app knows about a callsign: country, grid, distance, and whether it is already in the log.</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>部分設定值，採白名單。只有明確列出的鍵才會出現。</t>
+          <t>App 對某個呼號所知的資訊：國家、網格、距離，以及是否已在通聯記錄中。</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>Whitelist, not blacklist — 用黑名單的話，日後新增一個含密碼的設定就會自動外洩且無人察覺。第三方憑證（Cloudlog、QRZ）永遠不在其中。</t>
+          <t>Grid comes from the app's own CallsignQTH cache — 沒有查過的呼號會回 null。</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>/api/v1/stream</t>
+          <t>/api/v1/config</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>events (decode,rig,qso,log,status), since, token</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>stream.sse</t>
+          <t>config.read</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1506,17 +1506,17 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>Server-sent events. Each subscriber gets an independent queue, so multiple clients receive every event rather than sharing them out.</t>
+          <t>Selected settings, by whitelist. Only explicitly listed keys are exposed.</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>事件串流（SSE）。每個訂閱者有獨立佇列，多個客戶端各自收到完整事件，不會互相瓜分。</t>
+          <t>部分設定值，採白名單。只有明確列出的鍵才會出現。</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>EventSource cannot set headers, so this endpoint also accepts ?token= （瀏覽器規格限制）。收到 dropped 事件代表你的客戶端跟不上產生速度。</t>
+          <t>Whitelist, not blacklist — 用黑名單的話，日後新增一個含密碼的設定就會自動外洩且無人察覺。第三方憑證（Cloudlog、QRZ）永遠不在其中。</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>/api/v1/map/tile/{z}/{x}/{y}</t>
+          <t>/api/v1/stream</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>token</t>
+          <t>events (decode,rig,qso,log,status), since, token</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>map.tiles</t>
+          <t>stream.sse</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>Offline world map tile (JPEG) from the archive bundled in the app, so a map works with no internet connection. Zoom 0-4 only.</t>
+          <t>Server-sent events. Each subscriber gets an independent queue, so multiple clients receive every event rather than sharing them out.</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>離線世界地圖圖磚（JPEG），來自 App 內建的圖磚檔，沒有網路也能畫地圖。僅支援 zoom 0-4。</t>
+          <t>事件串流（SSE）。每個訂閱者有獨立佇列，多個客戶端各自收到完整事件，不會互相瓜分。</t>
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>Accepts ?token= so it can be used directly as an &lt;img&gt; source。此端點刻意不寫入稽核記錄，否則十幾個圖磚請求會把真正該看的存取洗掉。</t>
+          <t>EventSource cannot set headers, so this endpoint also accepts ?token= （瀏覽器規格限制）。收到 dropped 事件代表你的客戶端跟不上產生速度。</t>
         </is>
       </c>
     </row>
@@ -1596,17 +1596,17 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>/api/v1/audit</t>
+          <t>/api/v1/map/tile/{z}/{x}/{y}</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>limit</t>
+          <t>token</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>readonly</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>audit.read</t>
+          <t>map.tiles</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1636,17 +1636,17 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>Recent API access log, newest first. Requires a full-access token because entries contain each caller's IP and access history. NOT gated by the remote-control switch: being unable to look at what just happened right after switching remote control off would be exactly the wrong behaviour.</t>
+          <t>Offline world map tile (JPEG) from the archive bundled in the app, so a map works with no internet connection. Zoom 0-4 only.</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>近期的 API 存取記錄，由新到舊。需要 full token，因為記錄含每個呼叫者的 IP 與存取歷史。不受遠端控制開關影響：使用者發現異狀而關掉遠端控制之後，正是最需要查得到剛才發生什麼的時候。</t>
+          <t>離線世界地圖圖磚（JPEG），來自 App 內建的圖磚檔，沒有網路也能畫地圖。僅支援 zoom 0-4。</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>Ring buffer of 200 — held == capacity 表示更早的存取已被丟棄，這份清單不是完整歷史。讀取本身會被記錄，因此不要輪詢。</t>
+          <t>Accepts ?token= so it can be used directly as an &lt;img&gt; source。此端點刻意不寫入稽核記錄，否則十幾個圖磚請求會把真正該看的存取洗掉。</t>
         </is>
       </c>
     </row>
@@ -1661,120 +1661,120 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
+          <t>/api/v1/audit</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>limit</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>audit.read</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>26.0801</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>Recent API access log, newest first. Requires a full-access token because entries contain each caller's IP and access history. NOT gated by the remote-control switch: being unable to look at what just happened right after switching remote control off would be exactly the wrong behaviour.</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>近期的 API 存取記錄，由新到舊。需要 full token，因為記錄含每個呼叫者的 IP 與存取歷史。不受遠端控制開關影響：使用者發現異狀而關掉遠端控制之後，正是最需要查得到剛才發生什麼的時候。</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>Ring buffer of 200 — held == capacity 表示更早的存取已被丟棄，這份清單不是完整歷史。讀取本身會被記錄，因此不要輪詢。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="86" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
           <t>/api/v1/openapi.json</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>readonly</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>26.0801</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>Machine-readable OpenAPI description of this API.</t>
         </is>
       </c>
-      <c r="L16" s="4" t="inlineStr">
+      <c r="L17" s="4" t="inlineStr">
         <is>
           <t>本 API 的 OpenAPI 描述（機器可讀）。</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17" ht="86" customHeight="1">
-      <c r="A17" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>/api/v1/tx/stop</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>— (empty body)</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>control.tx</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>26.0801</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>Supported</t>
-        </is>
-      </c>
-      <c r="K17" s="6" t="inlineStr">
-        <is>
-          <t>Stop transmitting. Succeeds in EVERY state, including when nothing is transmitting and when the transmitter is not initialised — the caller's goal (nothing on the air) is already met, so that is not an error. Use the 'changed' field to tell 'I stopped a transmission' from 'nothing was running'.</t>
-        </is>
-      </c>
-      <c r="L17" s="6" t="inlineStr">
-        <is>
-          <t>停止發射。任何狀態下都成功，包含本來就沒在發射、以及發射器尚未初始化——呼叫者要的條件（沒有東西在空中）那時已經滿足，回錯誤只會讓對方重試。用 changed 欄位分辨「停下了一個發射」與「本來就沒在發」。</t>
-        </is>
-      </c>
-      <c r="M17" s="6" t="inlineStr">
-        <is>
-          <t>Stop must never fail on a precondition — 那會讓它在最需要的時候不能用。</t>
-        </is>
-      </c>
+      <c r="M17" s="4" t="inlineStr"/>
     </row>
     <row r="18" ht="86" customHeight="1">
       <c r="A18" s="6" t="n">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/tx/activate</t>
+          <t>/api/v1/tx/stop</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>body: {"activated": true|false}</t>
+          <t>— (empty body)</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -1827,17 +1827,17 @@
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t>Enable or disable transmission. The 'activated' field is required and is never defaulted — guessing it would start a transmission on a malformed request. The response reports the ACTUAL state, not the request: the app can refuse (for example while a mandatory update is pending), in which case 'blocked' is true.</t>
+          <t>Stop transmitting. Succeeds in EVERY state, including when nothing is transmitting and when the transmitter is not initialised — the caller's goal (nothing on the air) is already met, so that is not an error. Use the 'changed' field to tell 'I stopped a transmission' from 'nothing was running'.</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
         <is>
-          <t>開啟或關閉發射。activated 欄位為必填且不套用預設值——猜成 true 會讓一個打錯的請求開始發射。回應帶的是實際狀態而非請求值：App 可能拒絕（例如必要更新尚未完成），此時 blocked 為 true。</t>
+          <t>停止發射。任何狀態下都成功，包含本來就沒在發射、以及發射器尚未初始化——呼叫者要的條件（沒有東西在空中）那時已經滿足，回錯誤只會讓對方重試。用 changed 欄位分辨「停下了一個發射」與「本來就沒在發」。</t>
         </is>
       </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
-          <t>Goes through the app's own state machine, so it inherits every guard already there — 不自行改旗標。</t>
+          <t>Stop must never fail on a precondition — 那會讓它在最需要的時候不能用。</t>
         </is>
       </c>
     </row>
@@ -1852,12 +1852,12 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/tx/call</t>
+          <t>/api/v1/tx/activate</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>body: {"callsign": "JA1ABC", "activate": false}</t>
+          <t>body: {"activated": true|false}</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -1892,19 +1892,17 @@
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>Set the station to call. Only accepts a callsign that actually appears in the recent decodes — you can only call a station the app has heard. The slot, audio frequency and signal report are taken from that decode, so the caller supplies only the callsign.
-Does NOT start transmitting by default; pass activate:true for that.</t>
+          <t>Enable or disable transmission. The 'activated' field is required and is never defaulted — guessing it would start a transmission on a malformed request. The response reports the ACTUAL state, not the request: the app can refuse (for example while a mandatory update is pending), in which case 'blocked' is true.</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
-          <t>設定呼叫對象。只接受最近解碼中確實出現過的呼號——只能呼叫 App 實際聽到的電台。時序、音訊頻率與信號報告都取自那則解碼，呼叫者只需要給呼號。
-預設&lt;b&gt;不&lt;/b&gt;開始發射，需要時帶 activate:true。</t>
+          <t>開啟或關閉發射。activated 欄位為必填且不套用預設值——猜成 true 會讓一個打錯的請求開始發射。回應帶的是實際狀態而非請求值：App 可能拒絕（例如必要更新尚未完成），此時 blocked 為 true。</t>
         </is>
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
-          <t>Allowing an arbitrary string would let one typo transmit at a station that is not there — 那不只是無效發射。回 bad_request 時訊息會說明是「沒聽到這個呼號」而非格式錯誤，呼叫者才知道該等下一輪解碼。遙測與自由文字訊息不可呼叫，與解碼畫面的規則相同。</t>
+          <t>Goes through the app's own state machine, so it inherits every guard already there — 不自行改旗標。</t>
         </is>
       </c>
     </row>
@@ -1919,12 +1917,12 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/tx/cq</t>
+          <t>/api/v1/tx/call</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>body: {"activate": false}</t>
+          <t>body: {"callsign": "JA1ABC", "activate": false}</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -1959,17 +1957,19 @@
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>Go back to calling CQ. Does NOT start transmitting by default; pass activate:true for that.</t>
+          <t>Set the station to call. Only accepts a callsign that actually appears in the recent decodes — you can only call a station the app has heard. The slot, audio frequency and signal report are taken from that decode, so the caller supplies only the callsign.
+Does NOT start transmitting by default; pass activate:true for that.</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
-          <t>回到呼叫 CQ。預設&lt;b&gt;不&lt;/b&gt;開始發射，需要時帶 activate:true。</t>
+          <t>設定呼叫對象。只接受最近解碼中確實出現過的呼號——只能呼叫 App 實際聽到的電台。時序、音訊頻率與信號報告都取自那則解碼，呼叫者只需要給呼號。
+預設&lt;b&gt;不&lt;/b&gt;開始發射，需要時帶 activate:true。</t>
         </is>
       </c>
       <c r="M20" s="6" t="inlineStr">
         <is>
-          <t>Fails with busy if no callsign is configured in the app — resetToCQ() 在那種情況下會靜默跳過，回 ok 會讓呼叫者以為設定成功了。</t>
+          <t>Allowing an arbitrary string would let one typo transmit at a station that is not there — 那不只是無效發射。回 bad_request 時訊息會說明是「沒聽到這個呼號」而非格式錯誤，呼叫者才知道該等下一輪解碼。遙測與自由文字訊息不可呼叫，與解碼畫面的規則相同。</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/control/band</t>
+          <t>/api/v1/tx/cq</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>body: {"band": 14074000}</t>
+          <t>body: {"activate": false}</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>control.radio</t>
+          <t>control.tx</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
@@ -2024,17 +2024,17 @@
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>Change the operating frequency. Only accepts a frequency that exists in the band list for the current mode — allowing an arbitrary value would let a plugin put the radio outside the amateur bands, and the radio may well comply. Follows exactly the same path as the app's own frequency dialog, so it introduces no new per-model CAT risk. Refused while transmitting: changing frequency mid-transmission moves the carrier while it is on the air.</t>
+          <t>Go back to calling CQ. Does NOT start transmitting by default; pass activate:true for that.</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
-          <t>切換操作頻率。只接受目前模式的波段清單中存在的頻率——允許任意值等於讓外掛把電台調到業餘頻段之外，而電台可能照做。走與 App 頻率清單完全相同的路徑，因此不會引入新的機型風險。發射中拒絕：發射途中改頻率會讓載波在空中位移。</t>
+          <t>回到呼叫 CQ。預設&lt;b&gt;不&lt;/b&gt;開始發射，需要時帶 activate:true。</t>
         </is>
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
-          <t>radioCommanded tells you whether the radio was actually commanded — VOX/藍牙模式下 App 只改自己的設定，使用者仍須手動轉電台，不講清楚會以為換好了。</t>
+          <t>Fails with busy if no callsign is configured in the app — resetToCQ() 在那種情況下會靜默跳過，回 ok 會讓呼叫者以為設定成功了。</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/control/mode</t>
+          <t>/api/v1/control/band</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>body: {"mode": "FT8"}</t>
+          <t>body: {"band": 14074000}</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -2089,17 +2089,17 @@
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t>Switch between FT8, FT4 and FT2. This is the app's timing mode and sends no command to the radio, but it DOES change the operating frequency: each mode has its own band list and the nearest entry is selected. The response carries the resulting frequency so the caller need not guess. Refused while transmitting.</t>
+          <t>Change the operating frequency. Only accepts a frequency that exists in the band list for the current mode — allowing an arbitrary value would let a plugin put the radio outside the amateur bands, and the radio may well comply. Follows exactly the same path as the app's own frequency dialog, so it introduces no new per-model CAT risk. Refused while transmitting: changing frequency mid-transmission moves the carrier while it is on the air.</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
-          <t>切換 FT8／FT4／FT2。這是 App 內部的時序模式，不對電台送出指令，但會連帶改變操作頻率：各模式的波段清單不同，切換後會挑最接近的那一個。回應帶回新頻率，呼叫者不必自己猜。發射中拒絕。</t>
+          <t>切換操作頻率。只接受目前模式的波段清單中存在的頻率——允許任意值等於讓外掛把電台調到業餘頻段之外，而電台可能照做。走與 App 頻率清單完全相同的路徑，因此不會引入新的機型風險。發射中拒絕：發射途中改頻率會讓載波在空中位移。</t>
         </is>
       </c>
       <c r="M22" s="6" t="inlineStr">
         <is>
-          <t>Changing the timing mode mid-transmission would truncate the signal — 時序模式決定發射的長度與邊界。 CAUTION: switching modes back and forth DRIFTS the frequency. The nearest entry in the new mode's band list is chosen, so FT8 14.074 → FT4 → FT2 → FT8 lands on 14.090, not back on 14.074. This is the app's existing behaviour, not specific to the API — 但透過 API 快速連切會很明顯。Read the 'band' field in the response and set it explicitly with /control/band if you need a particular frequency.</t>
+          <t>radioCommanded tells you whether the radio was actually commanded — VOX/藍牙模式下 App 只改自己的設定，使用者仍須手動轉電台，不講清楚會以為換好了。</t>
         </is>
       </c>
     </row>
@@ -2114,129 +2114,194 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
+          <t>/api/v1/control/mode</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>body: {"mode": "FT8"}</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>control.radio</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>26.0801</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>Switch between FT8, FT4 and FT2. This is the app's timing mode and sends no command to the radio, but it DOES change the operating frequency: each mode has its own band list and the nearest entry is selected. The response carries the resulting frequency so the caller need not guess. Refused while transmitting.</t>
+        </is>
+      </c>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>切換 FT8／FT4／FT2。這是 App 內部的時序模式，不對電台送出指令，但會連帶改變操作頻率：各模式的波段清單不同，切換後會挑最接近的那一個。回應帶回新頻率，呼叫者不必自己猜。發射中拒絕。</t>
+        </is>
+      </c>
+      <c r="M23" s="6" t="inlineStr">
+        <is>
+          <t>Changing the timing mode mid-transmission would truncate the signal — 時序模式決定發射的長度與邊界。 CAUTION: switching modes back and forth DRIFTS the frequency. The nearest entry in the new mode's band list is chosen, so FT8 14.074 → FT4 → FT2 → FT8 lands on 14.090, not back on 14.074. This is the app's existing behaviour, not specific to the API — 但透過 API 快速連切會很明顯。Read the 'band' field in the response and set it explicitly with /control/band if you need a particular frequency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="86" customHeight="1">
+      <c r="A24" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
           <t>/api/v1/config</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>body: {"key": "antenna", "value": "EFHW 20m"}</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>full</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
+      <c r="G24" s="7" t="inlineStr">
         <is>
           <t>config.write</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>26.0801</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="J23" s="6" t="inlineStr">
+      <c r="J24" s="6" t="inlineStr">
         <is>
           <t>Supported</t>
         </is>
       </c>
-      <c r="K23" s="6" t="inlineStr">
+      <c r="K24" s="6" t="inlineStr">
         <is>
           <t>Change one setting. The writable list is deliberately much smaller than the readable one — being able to read a value does not mean it is safe for someone else to change it. Writable: noreplylimit, finishretrylimit, antenna.
 One key per request: a batch that half-succeeds leaves a state nobody can describe.</t>
         </is>
       </c>
-      <c r="L23" s="6" t="inlineStr">
+      <c r="L24" s="6" t="inlineStr">
         <is>
           <t>修改一項設定。可寫清單刻意比可讀清單小得多——能讀不代表別人改掉它是安全的。可寫的是 noreplylimit、finishretrylimit、antenna。
 一次只改一個鍵：批次修改在部分失敗時會留下說不清的中間狀態。</t>
         </is>
       </c>
-      <c r="M23" s="6" t="inlineStr">
+      <c r="M24" s="6" t="inlineStr">
         <is>
           <t>Radio connection settings (model/baudrate/connectmode) are NOT writable — 改了會斷開電台連線而遠端無法接回來，等於自斷後路。callsign 是法規識別、功率上限與 SWR 告警是安全限制、pttdelay 影響發射時序，一律不開放。頻率請用 /control/band（走那裡才會連帶命令電台換頻）。回應的 value 是實際生效的值，可能已被夾到合法範圍內。</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="86" customHeight="1">
-      <c r="A24" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
+    <row r="25" ht="86" customHeight="1">
+      <c r="A25" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>/api/v1/tx/freetext</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>full</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G24" s="9" t="inlineStr">
+      <c r="G25" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>26.0801</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
+      <c r="I25" s="8" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="J24" s="8" t="inlineStr">
+      <c r="J25" s="8" t="inlineStr">
         <is>
           <t>Not implemented (by design)</t>
         </is>
       </c>
-      <c r="K24" s="8" t="inlineStr">
+      <c r="K25" s="8" t="inlineStr">
         <is>
           <t>Always returns 501 not_implemented. Free text can put arbitrary content on the air under the licence holder's callsign, and that responsibility cannot be delimited by software. The path is reserved and documented so that plugin authors can tell a deliberate decision from a missing feature.</t>
         </is>
       </c>
-      <c r="L24" s="8" t="inlineStr">
+      <c r="L25" s="8" t="inlineStr">
         <is>
           <t>固定回 501 not_implemented。自由文字可以用執照持有人的呼號送出任意內容，而內容責任無法由軟體界定。此路徑保留並寫入文件，讓外掛作者能分辨「刻意不開放」與「功能還沒做」。</t>
         </is>
       </c>
-      <c r="M24" s="8" t="inlineStr">
+      <c r="M25" s="8" t="inlineStr">
         <is>
           <t>Returning 404 would be read as 'your app is too old' — 那是錯的訊息。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M24"/>
+  <autoFilter ref="A1:M25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2619,7 +2684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2899,6 +2964,23 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>ui.state</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Which screen is showing and the text on it</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>目前顯示的畫面與畫面上的文字</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
